--- a/output/CLFS_newformat_validated.xlsx
+++ b/output/CLFS_newformat_validated.xlsx
@@ -4025,7 +4025,7 @@
           <t>Self-employed</t>
         </is>
       </c>
-      <c r="CF4" t="n">
+      <c r="CF4" s="2" t="n">
         <v>44</v>
       </c>
       <c r="CG4" s="1" t="inlineStr">
